--- a/komnata_auto_export.xlsx
+++ b/komnata_auto_export.xlsx
@@ -21,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -51,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,15 +478,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prod</t>
+          <t>basen 2 0B</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>przeniesiony na 0A</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,27 +505,27 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-01 10:17:26</t>
+          <t>2026-05-04 16:36:54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-05-01 10:17:26</t>
+          <t>2026-05-04 16:38:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>produkt</t>
+          <t>basen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -536,60 +543,56 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-01 10:02:28</t>
+          <t>2026-05-04 16:36:20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-01 10:13:56</t>
+          <t>2026-05-04 16:36:31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>produkt</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>pro +++ ---</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Regał 3</t>
+          <t>regał 100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0B</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-01 09:30:42</t>
+          <t>2026-05-04 16:06:55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-05-01 10:01:18</t>
+          <t>2026-05-04 16:10:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>produkt 1.05</t>
+          <t>produkt</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -612,12 +615,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-01 09:25:48</t>
+          <t>2026-05-01 11:30:42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-05-01 09:59:34</t>
+          <t>2026-05-04 16:17:53</t>
         </is>
       </c>
     </row>
@@ -640,18 +643,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0B</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-04-30 14:55:06</t>
+          <t>2026-04-30 16:55:06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-30 14:55:06</t>
+          <t>2026-05-04 16:17:18</t>
         </is>
       </c>
     </row>
@@ -680,12 +683,12 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:23</t>
+          <t>2026-04-30 16:50:23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-30 14:50:23</t>
+          <t>2026-04-30 16:50:23</t>
         </is>
       </c>
     </row>
@@ -714,12 +717,12 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-04-30 14:41:45</t>
+          <t>2026-04-30 16:41:45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-30 14:41:45</t>
+          <t>2026-04-30 16:41:45</t>
         </is>
       </c>
     </row>
@@ -746,18 +749,18 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-04-29 14:56:37</t>
+          <t>2026-04-29 16:56:37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-29 14:58:46</t>
+          <t>2026-05-04 16:11:48</t>
         </is>
       </c>
     </row>
@@ -790,12 +793,12 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-04-29 14:22:35</t>
+          <t>2026-04-29 16:22:35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-29 14:31:30</t>
+          <t>2026-04-29 16:31:30</t>
         </is>
       </c>
     </row>
@@ -828,12 +831,12 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-04-14 02:45:55</t>
+          <t>2026-04-14 04:45:55</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-29 14:31:10</t>
+          <t>2026-04-29 16:31:10</t>
         </is>
       </c>
     </row>
@@ -862,12 +865,12 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-04-14 02:41:43</t>
+          <t>2026-04-14 04:41:43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-14 02:41:43</t>
+          <t>2026-04-14 04:41:43</t>
         </is>
       </c>
     </row>
@@ -896,12 +899,12 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-04-14 02:07:38</t>
+          <t>2026-04-14 04:07:38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-14 02:07:38</t>
+          <t>2026-04-14 04:07:38</t>
         </is>
       </c>
     </row>
@@ -938,12 +941,12 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-04-14 01:50:45</t>
+          <t>2026-04-14 03:50:45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-29 14:31:59</t>
+          <t>2026-04-29 16:31:59</t>
         </is>
       </c>
     </row>
@@ -972,12 +975,12 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-04-14 01:47:23</t>
+          <t>2026-04-14 03:47:23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-14 01:47:23</t>
+          <t>2026-04-14 03:47:23</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1009,12 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-04-14 01:37:52</t>
+          <t>2026-04-14 03:37:52</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-14 01:37:52</t>
+          <t>2026-04-14 03:37:52</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1063,11 @@
           <t>1 A</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="3">
@@ -1078,13 +1079,11 @@
           <t>1 B</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="4">
@@ -1096,13 +1095,11 @@
           <t>1 C</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="5">
@@ -1114,13 +1111,11 @@
           <t>2 A</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="6">
@@ -1132,13 +1127,11 @@
           <t>2 B</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="7">
@@ -1150,13 +1143,11 @@
           <t>2 C</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="8">
@@ -1168,13 +1159,11 @@
           <t>3 A</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="9">
@@ -1186,13 +1175,11 @@
           <t>3 B</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="10">
@@ -1204,13 +1191,11 @@
           <t>3 C</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="11">
@@ -1222,13 +1207,11 @@
           <t>4 A</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="12">
@@ -1240,13 +1223,11 @@
           <t>4 B</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="13">
@@ -1258,13 +1239,11 @@
           <t>4 C</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="14">
@@ -1276,13 +1255,11 @@
           <t>5 A</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="15">
@@ -1294,13 +1271,11 @@
           <t>5 B</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="16">
@@ -1312,13 +1287,11 @@
           <t>5 C</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="17">
@@ -1330,13 +1303,11 @@
           <t>6 A</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="18">
@@ -1348,13 +1319,11 @@
           <t>6 B</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="19">
@@ -1366,13 +1335,11 @@
           <t>6 C</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-01 20:54:03</t>
-        </is>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46113.87086805556</v>
       </c>
     </row>
     <row r="20">
@@ -1384,13 +1351,11 @@
           <t>Bez sektora</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-13 18:37:22</t>
-        </is>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46125.77594907407</v>
       </c>
     </row>
   </sheetData>
@@ -1448,13 +1413,11 @@
           <t>Bez regału</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-13 18:37:22</t>
-        </is>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46125.77594907407</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -1467,13 +1430,11 @@
           <t>Regał 1</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -1489,13 +1450,11 @@
           <t>Regał 2</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -1511,13 +1470,11 @@
           <t>Regał 3</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1533,13 +1490,11 @@
           <t>Regał 4</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1555,13 +1510,11 @@
           <t>Regał 5</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -1577,13 +1530,11 @@
           <t>Regał 55</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:18</t>
-        </is>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46126.01340277777</v>
       </c>
       <c r="E8" t="n">
         <v>34</v>
@@ -1603,13 +1554,11 @@
           <t>Regał 6</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1625,13 +1574,11 @@
           <t>Regał 7</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-04-13 18:56:10</t>
-        </is>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46125.78900462963</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1647,13 +1594,11 @@
           <t>Regał 8</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:18</t>
-        </is>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46126.01340277777</v>
       </c>
       <c r="E11" t="n">
         <v>20</v>
@@ -1673,13 +1618,11 @@
           <t>Regał 88</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:18</t>
-        </is>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46126.01340277777</v>
       </c>
       <c r="E12" t="n">
         <v>68</v>
@@ -1699,13 +1642,11 @@
           <t>Rozszerzenie 0-5 A,B,C</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46139.60133101852</v>
       </c>
       <c r="E13" t="n">
         <v>270</v>
@@ -1725,13 +1666,11 @@
           <t>Standard 0-5 A,B</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46139.60133101852</v>
       </c>
       <c r="E14" t="n">
         <v>269</v>
@@ -1751,13 +1690,11 @@
           <t>regał 100</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:18</t>
-        </is>
+      <c r="C15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46126.01340277777</v>
       </c>
       <c r="E15" t="n">
         <v>63</v>
@@ -1849,13 +1786,11 @@
           <t>TEST</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-04-13 19:09:58</t>
-        </is>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>46125.79858796296</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1818,11 @@
           <t>TEST</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-04-13 19:00:28</t>
-        </is>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>46125.79199074074</v>
       </c>
     </row>
     <row r="4">
@@ -1917,13 +1850,11 @@
           <t>Czerwono niebieski z narzędziami warsztat</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-04-13 20:05:08</t>
-        </is>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>46125.83689814815</v>
       </c>
     </row>
     <row r="5">
@@ -1951,13 +1882,11 @@
           <t>Układ rozszerzony o dodatkowy poziom C.</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>46146.56452973586</v>
       </c>
     </row>
     <row r="6">
@@ -1985,13 +1914,11 @@
           <t>Domyślny układ startowy dla każdego regału.</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>46146.56452973586</v>
       </c>
     </row>
     <row r="7">
@@ -2019,13 +1946,11 @@
           <t>test</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-04-13 19:58:15</t>
-        </is>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>46125.83211805556</v>
       </c>
     </row>
   </sheetData>
@@ -2099,13 +2024,11 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G2" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="3">
@@ -2128,13 +2051,11 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" t="b">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G3" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="4">
@@ -2157,13 +2078,11 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G4" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="5">
@@ -2186,13 +2105,11 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G5" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="6">
@@ -2215,13 +2132,11 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" t="b">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G6" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="7">
@@ -2244,13 +2159,11 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G7" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="8">
@@ -2273,13 +2186,11 @@
       <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="9">
@@ -2302,13 +2213,11 @@
       <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="10">
@@ -2331,13 +2240,11 @@
       <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="11">
@@ -2360,13 +2267,11 @@
       <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="12">
@@ -2389,13 +2294,11 @@
       <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="13">
@@ -2418,13 +2321,11 @@
       <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="14">
@@ -2447,13 +2348,11 @@
       <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="15">
@@ -2476,13 +2375,11 @@
       <c r="E15" t="n">
         <v>8</v>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="16">
@@ -2505,13 +2402,11 @@
       <c r="E16" t="n">
         <v>9</v>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="17">
@@ -2534,13 +2429,11 @@
       <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="18">
@@ -2563,13 +2456,11 @@
       <c r="E18" t="n">
         <v>11</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="19">
@@ -2592,13 +2483,11 @@
       <c r="E19" t="n">
         <v>12</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="20">
@@ -2621,13 +2510,11 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="b">
         <v>0</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G20" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="21">
@@ -2650,13 +2537,11 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="b">
         <v>0</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G21" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="22">
@@ -2679,13 +2564,11 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="b">
         <v>0</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G22" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="23">
@@ -2708,13 +2591,11 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="b">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G23" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="24">
@@ -2737,13 +2618,11 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="b">
         <v>0</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G24" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="25">
@@ -2766,13 +2645,11 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="b">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G25" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="26">
@@ -2795,13 +2672,11 @@
       <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="27">
@@ -2824,13 +2699,11 @@
       <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="28">
@@ -2853,13 +2726,11 @@
       <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="29">
@@ -2882,13 +2753,11 @@
       <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="30">
@@ -2911,13 +2780,11 @@
       <c r="E30" t="n">
         <v>5</v>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="31">
@@ -2940,13 +2807,11 @@
       <c r="E31" t="n">
         <v>6</v>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="32">
@@ -2969,13 +2834,11 @@
       <c r="E32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="33">
@@ -2998,13 +2861,11 @@
       <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="34">
@@ -3027,13 +2888,11 @@
       <c r="E34" t="n">
         <v>9</v>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="35">
@@ -3056,13 +2915,11 @@
       <c r="E35" t="n">
         <v>10</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="36">
@@ -3085,13 +2942,11 @@
       <c r="E36" t="n">
         <v>11</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="37">
@@ -3114,13 +2969,11 @@
       <c r="E37" t="n">
         <v>12</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="38">
@@ -3143,13 +2996,11 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" t="b">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G38" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="39">
@@ -3172,13 +3023,11 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39" t="b">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G39" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="40">
@@ -3201,13 +3050,11 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40" t="b">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G40" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="41">
@@ -3230,13 +3077,11 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41" t="b">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G41" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="42">
@@ -3259,13 +3104,11 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" t="b">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G42" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="43">
@@ -3288,13 +3131,11 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" t="b">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G43" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="44">
@@ -3317,13 +3158,11 @@
       <c r="E44" t="n">
         <v>1</v>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="45">
@@ -3346,13 +3185,11 @@
       <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="46">
@@ -3375,13 +3212,11 @@
       <c r="E46" t="n">
         <v>3</v>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="47">
@@ -3404,13 +3239,11 @@
       <c r="E47" t="n">
         <v>4</v>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="48">
@@ -3433,13 +3266,11 @@
       <c r="E48" t="n">
         <v>5</v>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="49">
@@ -3462,13 +3293,11 @@
       <c r="E49" t="n">
         <v>6</v>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="50">
@@ -3491,13 +3320,11 @@
       <c r="E50" t="n">
         <v>7</v>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="51">
@@ -3520,13 +3347,11 @@
       <c r="E51" t="n">
         <v>8</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="52">
@@ -3549,13 +3374,11 @@
       <c r="E52" t="n">
         <v>9</v>
       </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="53">
@@ -3578,13 +3401,11 @@
       <c r="E53" t="n">
         <v>10</v>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="54">
@@ -3607,13 +3428,11 @@
       <c r="E54" t="n">
         <v>11</v>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="55">
@@ -3636,13 +3455,11 @@
       <c r="E55" t="n">
         <v>12</v>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="56">
@@ -3665,13 +3482,11 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" t="b">
         <v>0</v>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G56" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="57">
@@ -3694,13 +3509,11 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57" t="b">
         <v>0</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G57" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="58">
@@ -3723,13 +3536,11 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" t="b">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G58" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="59">
@@ -3752,13 +3563,11 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59" t="b">
         <v>0</v>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G59" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="60">
@@ -3781,13 +3590,11 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60" t="b">
         <v>0</v>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G60" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="61">
@@ -3810,13 +3617,11 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61" t="b">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G61" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="62">
@@ -3839,13 +3644,11 @@
       <c r="E62" t="n">
         <v>1</v>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="63">
@@ -3868,13 +3671,11 @@
       <c r="E63" t="n">
         <v>2</v>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="64">
@@ -3897,13 +3698,11 @@
       <c r="E64" t="n">
         <v>3</v>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="65">
@@ -3926,13 +3725,11 @@
       <c r="E65" t="n">
         <v>4</v>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="66">
@@ -3955,13 +3752,11 @@
       <c r="E66" t="n">
         <v>5</v>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="67">
@@ -3984,13 +3779,11 @@
       <c r="E67" t="n">
         <v>6</v>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="68">
@@ -4013,13 +3806,11 @@
       <c r="E68" t="n">
         <v>7</v>
       </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="69">
@@ -4042,13 +3833,11 @@
       <c r="E69" t="n">
         <v>8</v>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="70">
@@ -4071,13 +3860,11 @@
       <c r="E70" t="n">
         <v>9</v>
       </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="71">
@@ -4100,13 +3887,11 @@
       <c r="E71" t="n">
         <v>10</v>
       </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="72">
@@ -4129,13 +3914,11 @@
       <c r="E72" t="n">
         <v>11</v>
       </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="73">
@@ -4158,13 +3941,11 @@
       <c r="E73" t="n">
         <v>12</v>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="74">
@@ -4187,13 +3968,11 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" t="b">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G74" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="75">
@@ -4216,13 +3995,11 @@
       <c r="E75" t="n">
         <v>0</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75" t="b">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G75" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="76">
@@ -4245,13 +4022,11 @@
       <c r="E76" t="n">
         <v>0</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76" t="b">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G76" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="77">
@@ -4274,13 +4049,11 @@
       <c r="E77" t="n">
         <v>0</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77" t="b">
         <v>0</v>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G77" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="78">
@@ -4303,13 +4076,11 @@
       <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78" t="b">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G78" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="79">
@@ -4332,13 +4103,11 @@
       <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79" t="b">
         <v>0</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G79" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="80">
@@ -4361,13 +4130,11 @@
       <c r="E80" t="n">
         <v>1</v>
       </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="81">
@@ -4390,13 +4157,11 @@
       <c r="E81" t="n">
         <v>2</v>
       </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="82">
@@ -4419,13 +4184,11 @@
       <c r="E82" t="n">
         <v>3</v>
       </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="83">
@@ -4448,13 +4211,11 @@
       <c r="E83" t="n">
         <v>4</v>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="84">
@@ -4477,13 +4238,11 @@
       <c r="E84" t="n">
         <v>5</v>
       </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="85">
@@ -4506,13 +4265,11 @@
       <c r="E85" t="n">
         <v>6</v>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="86">
@@ -4535,13 +4292,11 @@
       <c r="E86" t="n">
         <v>7</v>
       </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="87">
@@ -4564,13 +4319,11 @@
       <c r="E87" t="n">
         <v>8</v>
       </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="88">
@@ -4593,13 +4346,11 @@
       <c r="E88" t="n">
         <v>9</v>
       </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="89">
@@ -4622,13 +4373,11 @@
       <c r="E89" t="n">
         <v>10</v>
       </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="90">
@@ -4651,13 +4400,11 @@
       <c r="E90" t="n">
         <v>11</v>
       </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="91">
@@ -4680,13 +4427,11 @@
       <c r="E91" t="n">
         <v>12</v>
       </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="92">
@@ -4709,13 +4454,11 @@
       <c r="E92" t="n">
         <v>1</v>
       </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="93">
@@ -4738,13 +4481,11 @@
       <c r="E93" t="n">
         <v>2</v>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F93" t="b">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="94">
@@ -4767,13 +4508,11 @@
       <c r="E94" t="n">
         <v>3</v>
       </c>
-      <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="95">
@@ -4796,13 +4535,11 @@
       <c r="E95" t="n">
         <v>4</v>
       </c>
-      <c r="F95" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="96">
@@ -4825,13 +4562,11 @@
       <c r="E96" t="n">
         <v>5</v>
       </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="97">
@@ -4854,13 +4589,11 @@
       <c r="E97" t="n">
         <v>6</v>
       </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="98">
@@ -4883,13 +4616,11 @@
       <c r="E98" t="n">
         <v>7</v>
       </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="99">
@@ -4912,13 +4643,11 @@
       <c r="E99" t="n">
         <v>8</v>
       </c>
-      <c r="F99" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="100">
@@ -4941,13 +4670,11 @@
       <c r="E100" t="n">
         <v>9</v>
       </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="101">
@@ -4970,13 +4697,11 @@
       <c r="E101" t="n">
         <v>10</v>
       </c>
-      <c r="F101" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="102">
@@ -4999,13 +4724,11 @@
       <c r="E102" t="n">
         <v>11</v>
       </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F102" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="103">
@@ -5028,13 +4751,11 @@
       <c r="E103" t="n">
         <v>12</v>
       </c>
-      <c r="F103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="104">
@@ -5057,13 +4778,11 @@
       <c r="E104" t="n">
         <v>0</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104" t="b">
         <v>0</v>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G104" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="105">
@@ -5086,13 +4805,11 @@
       <c r="E105" t="n">
         <v>0</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105" t="b">
         <v>0</v>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G105" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="106">
@@ -5115,13 +4832,11 @@
       <c r="E106" t="n">
         <v>0</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106" t="b">
         <v>0</v>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G106" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="107">
@@ -5144,13 +4859,11 @@
       <c r="E107" t="n">
         <v>0</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107" t="b">
         <v>0</v>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G107" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="108">
@@ -5173,13 +4886,11 @@
       <c r="E108" t="n">
         <v>0</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108" t="b">
         <v>0</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G108" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="109">
@@ -5202,13 +4913,11 @@
       <c r="E109" t="n">
         <v>0</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109" t="b">
         <v>0</v>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="G109" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="110">
@@ -5231,13 +4940,11 @@
       <c r="E110" t="n">
         <v>1</v>
       </c>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="111">
@@ -5260,13 +4967,11 @@
       <c r="E111" t="n">
         <v>2</v>
       </c>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="112">
@@ -5289,13 +4994,11 @@
       <c r="E112" t="n">
         <v>3</v>
       </c>
-      <c r="F112" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="113">
@@ -5318,13 +5021,11 @@
       <c r="E113" t="n">
         <v>4</v>
       </c>
-      <c r="F113" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="114">
@@ -5347,13 +5048,11 @@
       <c r="E114" t="n">
         <v>5</v>
       </c>
-      <c r="F114" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="115">
@@ -5376,13 +5075,11 @@
       <c r="E115" t="n">
         <v>6</v>
       </c>
-      <c r="F115" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="116">
@@ -5405,13 +5102,11 @@
       <c r="E116" t="n">
         <v>7</v>
       </c>
-      <c r="F116" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="117">
@@ -5434,13 +5129,11 @@
       <c r="E117" t="n">
         <v>8</v>
       </c>
-      <c r="F117" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="118">
@@ -5463,13 +5156,11 @@
       <c r="E118" t="n">
         <v>9</v>
       </c>
-      <c r="F118" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="119">
@@ -5492,13 +5183,11 @@
       <c r="E119" t="n">
         <v>10</v>
       </c>
-      <c r="F119" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="120">
@@ -5521,13 +5210,11 @@
       <c r="E120" t="n">
         <v>11</v>
       </c>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="121">
@@ -5550,13 +5237,11 @@
       <c r="E121" t="n">
         <v>12</v>
       </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2026-04-01 21:31:25</t>
-        </is>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1" t="n">
+        <v>46113.89681712963</v>
       </c>
     </row>
     <row r="122">
@@ -5579,13 +5264,11 @@
       <c r="E122" t="n">
         <v>1</v>
       </c>
-      <c r="F122" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+      <c r="G122" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="123">
@@ -5608,13 +5291,11 @@
       <c r="E123" t="n">
         <v>2</v>
       </c>
-      <c r="F123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+      <c r="G123" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="124">
@@ -5637,13 +5318,11 @@
       <c r="E124" t="n">
         <v>3</v>
       </c>
-      <c r="F124" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="125">
@@ -5666,13 +5345,11 @@
       <c r="E125" t="n">
         <v>4</v>
       </c>
-      <c r="F125" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="126">
@@ -5695,13 +5372,11 @@
       <c r="E126" t="n">
         <v>5</v>
       </c>
-      <c r="F126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="127">
@@ -5724,13 +5399,11 @@
       <c r="E127" t="n">
         <v>6</v>
       </c>
-      <c r="F127" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F127" t="b">
+        <v>1</v>
+      </c>
+      <c r="G127" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="128">
@@ -5753,13 +5426,11 @@
       <c r="E128" t="n">
         <v>7</v>
       </c>
-      <c r="F128" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="129">
@@ -5782,13 +5453,11 @@
       <c r="E129" t="n">
         <v>8</v>
       </c>
-      <c r="F129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F129" t="b">
+        <v>1</v>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="130">
@@ -5811,13 +5480,11 @@
       <c r="E130" t="n">
         <v>9</v>
       </c>
-      <c r="F130" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F130" t="b">
+        <v>1</v>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="131">
@@ -5840,13 +5507,11 @@
       <c r="E131" t="n">
         <v>10</v>
       </c>
-      <c r="F131" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F131" t="b">
+        <v>1</v>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="132">
@@ -5869,13 +5534,11 @@
       <c r="E132" t="n">
         <v>11</v>
       </c>
-      <c r="F132" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F132" t="b">
+        <v>1</v>
+      </c>
+      <c r="G132" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="133">
@@ -5898,13 +5561,11 @@
       <c r="E133" t="n">
         <v>12</v>
       </c>
-      <c r="F133" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:14:59</t>
-        </is>
+      <c r="F133" t="b">
+        <v>1</v>
+      </c>
+      <c r="G133" s="1" t="n">
+        <v>46126.09373842592</v>
       </c>
     </row>
     <row r="134">
@@ -5927,13 +5588,11 @@
       <c r="E134" t="n">
         <v>1</v>
       </c>
-      <c r="F134" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F134" t="b">
+        <v>1</v>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="135">
@@ -5956,13 +5615,11 @@
       <c r="E135" t="n">
         <v>2</v>
       </c>
-      <c r="F135" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F135" t="b">
+        <v>1</v>
+      </c>
+      <c r="G135" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="136">
@@ -5985,13 +5642,11 @@
       <c r="E136" t="n">
         <v>3</v>
       </c>
-      <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="137">
@@ -6014,13 +5669,11 @@
       <c r="E137" t="n">
         <v>4</v>
       </c>
-      <c r="F137" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="138">
@@ -6043,13 +5696,11 @@
       <c r="E138" t="n">
         <v>5</v>
       </c>
-      <c r="F138" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F138" t="b">
+        <v>1</v>
+      </c>
+      <c r="G138" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="139">
@@ -6072,13 +5723,11 @@
       <c r="E139" t="n">
         <v>6</v>
       </c>
-      <c r="F139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F139" t="b">
+        <v>1</v>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="140">
@@ -6101,13 +5750,11 @@
       <c r="E140" t="n">
         <v>7</v>
       </c>
-      <c r="F140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F140" t="b">
+        <v>1</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="141">
@@ -6130,13 +5777,11 @@
       <c r="E141" t="n">
         <v>8</v>
       </c>
-      <c r="F141" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F141" t="b">
+        <v>1</v>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="142">
@@ -6159,13 +5804,11 @@
       <c r="E142" t="n">
         <v>9</v>
       </c>
-      <c r="F142" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F142" t="b">
+        <v>1</v>
+      </c>
+      <c r="G142" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="143">
@@ -6188,13 +5831,11 @@
       <c r="E143" t="n">
         <v>10</v>
       </c>
-      <c r="F143" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F143" t="b">
+        <v>1</v>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="144">
@@ -6217,13 +5858,11 @@
       <c r="E144" t="n">
         <v>1</v>
       </c>
-      <c r="F144" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F144" t="b">
+        <v>1</v>
+      </c>
+      <c r="G144" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="145">
@@ -6246,13 +5885,11 @@
       <c r="E145" t="n">
         <v>2</v>
       </c>
-      <c r="F145" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F145" t="b">
+        <v>1</v>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="146">
@@ -6275,13 +5912,11 @@
       <c r="E146" t="n">
         <v>3</v>
       </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+      <c r="G146" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="147">
@@ -6304,13 +5939,11 @@
       <c r="E147" t="n">
         <v>4</v>
       </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F147" t="b">
+        <v>1</v>
+      </c>
+      <c r="G147" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="148">
@@ -6333,13 +5966,11 @@
       <c r="E148" t="n">
         <v>5</v>
       </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F148" t="b">
+        <v>1</v>
+      </c>
+      <c r="G148" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="149">
@@ -6362,13 +5993,11 @@
       <c r="E149" t="n">
         <v>6</v>
       </c>
-      <c r="F149" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+      <c r="G149" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="150">
@@ -6391,13 +6020,11 @@
       <c r="E150" t="n">
         <v>7</v>
       </c>
-      <c r="F150" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F150" t="b">
+        <v>1</v>
+      </c>
+      <c r="G150" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="151">
@@ -6420,13 +6047,11 @@
       <c r="E151" t="n">
         <v>8</v>
       </c>
-      <c r="F151" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F151" t="b">
+        <v>1</v>
+      </c>
+      <c r="G151" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="152">
@@ -6449,13 +6074,11 @@
       <c r="E152" t="n">
         <v>9</v>
       </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F152" t="b">
+        <v>1</v>
+      </c>
+      <c r="G152" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="153">
@@ -6478,13 +6101,11 @@
       <c r="E153" t="n">
         <v>10</v>
       </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F153" t="b">
+        <v>1</v>
+      </c>
+      <c r="G153" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="154">
@@ -6507,13 +6128,11 @@
       <c r="E154" t="n">
         <v>1</v>
       </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+      <c r="G154" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="155">
@@ -6536,13 +6155,11 @@
       <c r="E155" t="n">
         <v>2</v>
       </c>
-      <c r="F155" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F155" t="b">
+        <v>1</v>
+      </c>
+      <c r="G155" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="156">
@@ -6565,13 +6182,11 @@
       <c r="E156" t="n">
         <v>3</v>
       </c>
-      <c r="F156" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F156" t="b">
+        <v>1</v>
+      </c>
+      <c r="G156" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="157">
@@ -6594,13 +6209,11 @@
       <c r="E157" t="n">
         <v>4</v>
       </c>
-      <c r="F157" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F157" t="b">
+        <v>1</v>
+      </c>
+      <c r="G157" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="158">
@@ -6623,13 +6236,11 @@
       <c r="E158" t="n">
         <v>5</v>
       </c>
-      <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F158" t="b">
+        <v>1</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="159">
@@ -6652,13 +6263,11 @@
       <c r="E159" t="n">
         <v>6</v>
       </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F159" t="b">
+        <v>1</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="160">
@@ -6681,13 +6290,11 @@
       <c r="E160" t="n">
         <v>7</v>
       </c>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F160" t="b">
+        <v>1</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="161">
@@ -6710,13 +6317,11 @@
       <c r="E161" t="n">
         <v>8</v>
       </c>
-      <c r="F161" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F161" t="b">
+        <v>1</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="162">
@@ -6739,13 +6344,11 @@
       <c r="E162" t="n">
         <v>9</v>
       </c>
-      <c r="F162" t="n">
-        <v>1</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F162" t="b">
+        <v>1</v>
+      </c>
+      <c r="G162" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="163">
@@ -6768,13 +6371,11 @@
       <c r="E163" t="n">
         <v>10</v>
       </c>
-      <c r="F163" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
+      <c r="G163" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="164">
@@ -6797,13 +6398,11 @@
       <c r="E164" t="n">
         <v>11</v>
       </c>
-      <c r="F164" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F164" t="b">
+        <v>1</v>
+      </c>
+      <c r="G164" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="165">
@@ -6826,13 +6425,11 @@
       <c r="E165" t="n">
         <v>12</v>
       </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F165" t="b">
+        <v>1</v>
+      </c>
+      <c r="G165" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="166">
@@ -6855,13 +6452,11 @@
       <c r="E166" t="n">
         <v>13</v>
       </c>
-      <c r="F166" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F166" t="b">
+        <v>1</v>
+      </c>
+      <c r="G166" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="167">
@@ -6884,13 +6479,11 @@
       <c r="E167" t="n">
         <v>14</v>
       </c>
-      <c r="F167" t="n">
-        <v>1</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F167" t="b">
+        <v>1</v>
+      </c>
+      <c r="G167" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="168">
@@ -6913,13 +6506,11 @@
       <c r="E168" t="n">
         <v>15</v>
       </c>
-      <c r="F168" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F168" t="b">
+        <v>1</v>
+      </c>
+      <c r="G168" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="169">
@@ -6942,13 +6533,11 @@
       <c r="E169" t="n">
         <v>16</v>
       </c>
-      <c r="F169" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F169" t="b">
+        <v>1</v>
+      </c>
+      <c r="G169" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="170">
@@ -6971,13 +6560,11 @@
       <c r="E170" t="n">
         <v>17</v>
       </c>
-      <c r="F170" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
+      <c r="G170" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="171">
@@ -7000,13 +6587,11 @@
       <c r="E171" t="n">
         <v>18</v>
       </c>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
+      <c r="G171" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="172">
@@ -7029,13 +6614,11 @@
       <c r="E172" t="n">
         <v>1</v>
       </c>
-      <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
+      <c r="G172" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="173">
@@ -7058,13 +6641,11 @@
       <c r="E173" t="n">
         <v>2</v>
       </c>
-      <c r="F173" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
+      <c r="G173" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="174">
@@ -7087,13 +6668,11 @@
       <c r="E174" t="n">
         <v>3</v>
       </c>
-      <c r="F174" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F174" t="b">
+        <v>1</v>
+      </c>
+      <c r="G174" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="175">
@@ -7116,13 +6695,11 @@
       <c r="E175" t="n">
         <v>4</v>
       </c>
-      <c r="F175" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="176">
@@ -7145,13 +6722,11 @@
       <c r="E176" t="n">
         <v>5</v>
       </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+      <c r="G176" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="177">
@@ -7174,13 +6749,11 @@
       <c r="E177" t="n">
         <v>6</v>
       </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+      <c r="G177" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="178">
@@ -7203,13 +6776,11 @@
       <c r="E178" t="n">
         <v>7</v>
       </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+      <c r="G178" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="179">
@@ -7232,13 +6803,11 @@
       <c r="E179" t="n">
         <v>8</v>
       </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="180">
@@ -7261,13 +6830,11 @@
       <c r="E180" t="n">
         <v>9</v>
       </c>
-      <c r="F180" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
+      <c r="G180" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="181">
@@ -7290,13 +6857,11 @@
       <c r="E181" t="n">
         <v>10</v>
       </c>
-      <c r="F181" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="182">
@@ -7319,13 +6884,11 @@
       <c r="E182" t="n">
         <v>11</v>
       </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
+      <c r="G182" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="183">
@@ -7348,13 +6911,11 @@
       <c r="E183" t="n">
         <v>12</v>
       </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:25:55</t>
-        </is>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
+      <c r="G183" s="1" t="n">
+        <v>46146.56455891582</v>
       </c>
     </row>
     <row r="184">
@@ -7377,13 +6938,11 @@
       <c r="E184" t="n">
         <v>1</v>
       </c>
-      <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+      <c r="G184" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="185">
@@ -7406,13 +6965,11 @@
       <c r="E185" t="n">
         <v>2</v>
       </c>
-      <c r="F185" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F185" t="b">
+        <v>1</v>
+      </c>
+      <c r="G185" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="186">
@@ -7435,13 +6992,11 @@
       <c r="E186" t="n">
         <v>3</v>
       </c>
-      <c r="F186" t="n">
-        <v>1</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F186" t="b">
+        <v>1</v>
+      </c>
+      <c r="G186" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="187">
@@ -7464,13 +7019,11 @@
       <c r="E187" t="n">
         <v>4</v>
       </c>
-      <c r="F187" t="n">
-        <v>1</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
+      <c r="G187" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="188">
@@ -7493,13 +7046,11 @@
       <c r="E188" t="n">
         <v>5</v>
       </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F188" t="b">
+        <v>1</v>
+      </c>
+      <c r="G188" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
     <row r="189">
@@ -7522,13 +7073,11 @@
       <c r="E189" t="n">
         <v>6</v>
       </c>
-      <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>2026-04-14 00:19:48</t>
-        </is>
+      <c r="F189" t="b">
+        <v>1</v>
+      </c>
+      <c r="G189" s="1" t="n">
+        <v>46126.01375</v>
       </c>
     </row>
   </sheetData>
@@ -7542,7 +7091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7579,66 +7128,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>edit</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Edytowano produkt: produkt</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-01 10:01:18</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>produkt</t>
-        </is>
-      </c>
+          <t>Usunięto produkt: produkt z - / Regał 1 / 0B</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46146.62820031736</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>move</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Przeniesiono: - / Regał 3 / 0A → - / Regał 3 / 0B</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-05-01 10:00:41</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>produkt</t>
-        </is>
-      </c>
+          <t>Usunięto produkt: produkt 1.05 z - / Regał 3 / 0B</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46146.61101563064</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7647,235 +7184,1101 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Przeniesiono: - / Regał 3 / 0B → - / Regał 3 / 0A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-05-01 09:59:34</t>
-        </is>
+          <t>Przeniesiono: - / Regał 1 / 0B → - / Regał 1 / 0A</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46146.6099627533</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>produkt 1.05</t>
+          <t>basen 2 0B</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Usunięto produkt: FARBA z - / Regał 1 / 0B</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-04-27 14:26:47</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>Przeniesiono: - / Regał 3 / 0B → - / Regał 3 / 0A</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46146.59575661521</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>produkt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dodano produkt: FARBA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:46:58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>Przeniesiono: - / Regał 3 / 0B → - / Regał 3 / 0A</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46146.59535390289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PRODUKT 30.04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dodano produkt: FARBA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:45:55</t>
-        </is>
+          <t>Przeniesiono: - / Regał 3 / 0A → - / Regał 3 / 0B</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46146.59502164606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FARBA</t>
+          <t>PRODUKT 30.04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dodano produkt: dRVA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:41:43</t>
-        </is>
+          <t>Przeniesiono: - / Regał 3 / 0B → - / Regał 3 / 0A</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46146.59480035921</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dRVA</t>
+          <t>PRODUKT 30.04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dodano produkt: niniin</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:07:38</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>niniin</t>
-        </is>
-      </c>
+          <t>Przeniesiono: - / Regał 3 / 0A → - / Regał 3 / 0B</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46146.59301652215</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dodano produkt: rag</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-04-14 01:50:45</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>rag</t>
-        </is>
-      </c>
+          <t>Przeniesiono: - / Regał 1 / 0A → - / Regał 1 / 0B</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46146.59266824531</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>create</t>
+          <t>move</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dodano produkt: test godziny</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-04-14 01:47:23</t>
-        </is>
+          <t>Przeniesiono: - / regał 100 / 0A → - / regał 100 / 1A</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46146.59153441474</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>test godziny</t>
+          <t>TEST KOPII</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>39</v>
+      </c>
+      <c r="B12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>edit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Edytowano produkt: pro +++ ---</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46146.59045220446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pro +++ ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>38</v>
+      </c>
+      <c r="B13" t="n">
+        <v>29</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: prod z - / Regał 1 / 0A</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46146.58947778282</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>37</v>
+      </c>
+      <c r="B14" t="n">
+        <v>30</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Przeniesiono: - / Regał 1 / 0A → - / regał 100 / 0A</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46146.58928392921</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pro +++ ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: rag z - / Regał 88 / 0A</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46139.51819289262</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rag</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>35</v>
+      </c>
+      <c r="B16" t="n">
+        <v>17</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: FARBA z - / Regał 3 / 1A</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46139.51812201423</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FARBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: dRVA z - / Regał 1 / 1A</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46139.51807713437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dRVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>33</v>
+      </c>
+      <c r="B18" t="n">
+        <v>18</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: FARBA z - / Regał 1 / 0B</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46139.51803034607</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: farba farba z - / REGAŁ 88 / 0B</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46139.51797926224</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>31</v>
+      </c>
+      <c r="B20" t="n">
         <v>2</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: olej test z - / REGAŁ 88 / 0A</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46139.5177913309</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>30</v>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: GARBA z - / REGAŁ 8 / 0B</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46139.51774289837</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: FARBA z - / REGAL 1 / 0B</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46139.51768968761</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: czas z - / REG 33 / 0A</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46139.51764404602</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: gc z - / MAŁY 113 / 0B</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46139.51759185173</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: farba z - / MALY 112 / 0A</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46139.51754041101</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: hey z - / MALY 112 / 0A</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46139.51747868842</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: czas czas z - / MAGAZYN / 0B</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46139.51742402339</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>edit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Edytowano produkt: produkt</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46143.41756944444</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>produkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Przeniesiono: - / Regał 3 / 0A → - / Regał 3 / 0B</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46143.4171412037</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>produkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>move</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Przeniesiono: - / Regał 3 / 0B → - / Regał 3 / 0A</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46143.41636574074</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>delete</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Usunięto produkt: FARBA z - / Regał 1 / 0B</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46139.60193287037</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B32" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Dodano produkt: GARBA</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46126.11753472222</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Dodano produkt: FARBA</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46126.11729166667</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" t="n">
+        <v>18</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Dodano produkt: FARBA</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46126.11594907408</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B35" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Dodano produkt: FARBA</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46126.11521990741</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>FARBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Dodano produkt: dRVA</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>46126.11230324074</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>dRVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>14</v>
+      </c>
+      <c r="B37" t="n">
+        <v>15</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Dodano produkt: farba</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>46126.10973379629</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Dodano produkt: farba</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>46126.10962962963</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Dodano produkt: hey</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>46126.10493055556</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B40" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Dodano produkt: czas test</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>46126.10375</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dodano produkt: czas czas</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>46126.09818287037</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dodano produkt: ga</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46126.09504629629</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Dodano produkt: gc</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>46126.09287037037</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Dodano produkt: czas</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46126.0919212963</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>6</v>
+      </c>
+      <c r="B45" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Dodano produkt: niniin</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46126.08863425926</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>niniin</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Dodano produkt: rag</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>46126.07690972222</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>rag</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Dodano produkt: test godziny</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>46126.07457175926</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>test godziny</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>create</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Dodano produkt: farba farba</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>46126.07100694445</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Dodano produkt: farba tgest</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-04-14 01:37:52</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E49" s="1" t="n">
+        <v>46126.06796296296</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>farba tgest</t>
         </is>
       </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>create</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Dodano produkt: olej test</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>46126.06627314815</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
